--- a/data/trans_dic/IP29A_R_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP29A_R_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 meses o más (tasa de respuesta: 97,51%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>59,8%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>58,26%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>59,01%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>47,17; 75,76</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>47,23; 69,09</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>49,68; 68,32</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>54,5%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57,16%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>55,66%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>46,06; 61,95</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>48,49; 65,54</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>49,59; 61,27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>75,91%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>69,48%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>58,54; 86,57</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>57,36; 78,61</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>63,66; 80,51</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>70,5%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>59,91%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>65,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>61,15; 78,27</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>50,78; 69,51</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>59,03; 71,31</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>63,57%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>60,53%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>62,14%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>58,18; 68,55</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>55,6; 65,02</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>58,83; 65,94</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -825,7 +498,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con lactancia materna exclusiva hasta los 6 meses o más (tasa de respuesta: 97,51%)</t>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 97,51%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.5979531695458891</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.5825716019475705</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.5901330768424921</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>37266</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>37550</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>74816</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.471655977285184</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.4723008173007623</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.4967866235972621</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>29395; 47214</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>30442; 44532</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>62982; 86615</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.7575643505450635</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.6909046986965449</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.6832057739821285</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.5449690019559771</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.5715913730894223</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.5566017765339693</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>67470</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>54918</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>122388</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.4606264095761183</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.484890099913028</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.4959122292525053</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>57028; 76702</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>46588; 62974</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>109043; 134731</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.6195403946809509</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.6554422980170452</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6127352453977811</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.7590746702507102</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.6947928869675768</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7290746185827032</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>50160</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>40178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>90337</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.5853585673217815</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.5736240391224962</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.6366066565026848</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>38680; 57203</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>33171; 45456</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>78880; 99761</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.8656581381736814</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.786076026107006</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.8051259679667061</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.7050198363008018</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.5990688067086055</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.6533682621319759</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>55264</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>44669</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>99933</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.6114641824871565</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.507845445603141</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.590323173777888</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>47931; 61355</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>37867; 51831</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>90291; 109071</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.7827170540943638</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.6951259208202742</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.7131089521708133</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>563</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.6357029408936093</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.6053233238990358</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.6214308097922201</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>210160</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>177314</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>387475</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.5818119974373586</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.5559971157819332</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.5883211579932394</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>192344; 226625</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>162865; 190448</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>366830; 411175</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.6855057575465572</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.6501605756714314</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.659441196747299</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con lactancia materna exclusiva hasta los 6 primeros meses de vida o más (tasa de respuesta: 97,51%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>64</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>37266</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>37550</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>74816</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>29395</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>30442</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>62982</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>47214</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>44532</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>86615</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>102</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>67470</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>54918</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>122388</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>57028</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>46588</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>109043</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>76702</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>62974</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>134731</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>50160</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>40178</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>90337</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>38680</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>33171</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>78880</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>57203</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>45456</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>99761</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>55264</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>44669</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>99933</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>47931</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>37867</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>90291</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>61355</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>51831</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>109071</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>294</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>269</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>210160</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>177314</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>387475</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>192344</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>162865</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>366830</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>226625</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>190448</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>411175</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>